--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-12).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-12).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>R$ 9.138,36</t>
-  </si>
-  <si>
-    <t>96.7</t>
-  </si>
-  <si>
-    <t>61.0</t>
-  </si>
-  <si>
-    <t>5.92</t>
-  </si>
-  <si>
-    <t>19.8</t>
+    <t>26</t>
+  </si>
+  <si>
+    <t>R$ 9.149,02</t>
+  </si>
+  <si>
+    <t>96.9</t>
+  </si>
+  <si>
+    <t>60.8</t>
+  </si>
+  <si>
+    <t>5.91</t>
+  </si>
+  <si>
+    <t>19.7</t>
   </si>
   <si>
     <t>7.1</t>
   </si>
   <si>
-    <t>6.2</t>
-  </si>
-  <si>
-    <t>34.9%</t>
-  </si>
-  <si>
-    <t>16.5%</t>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>35.0%</t>
+  </si>
+  <si>
+    <t>16.4%</t>
   </si>
   <si>
     <t>1.7%</t>
@@ -989,10 +989,10 @@
     <t>4.4%</t>
   </si>
   <si>
-    <t>2269.0</t>
-  </si>
-  <si>
-    <t>1863.0</t>
+    <t>2270.0</t>
+  </si>
+  <si>
+    <t>1864.0</t>
   </si>
   <si>
     <t>192.0</t>
@@ -1010,7 +1010,7 @@
     <t>15.0</t>
   </si>
   <si>
-    <t>700.0</t>
+    <t>701.0</t>
   </si>
   <si>
     <t>264.0</t>
@@ -10111,7 +10111,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -10141,18 +10141,30 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>11133.440000000001</v>
+      </c>
+      <c r="N58" s="6">
+        <v>125</v>
+      </c>
       <c r="O58" s="6">
         <v>97</v>
       </c>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>3.5377952755905513</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>16.395659375000001</v>
+      </c>
+      <c r="R58" s="8">
+        <v>7.3771474226804123</v>
+      </c>
       <c r="S58" s="8">
         <v>7</v>
       </c>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.40625</v>
+      </c>
       <c r="U58" s="9">
         <v>0.1134020618556701</v>
       </c>
@@ -18006,7 +18018,9 @@
       <c r="N111" s="6">
         <v>19</v>
       </c>
-      <c r="O111" s="6"/>
+      <c r="O111" s="6">
+        <v>17</v>
+      </c>
       <c r="P111" s="7">
         <v>4.1078947368421055</v>
       </c>
@@ -18016,31 +18030,75 @@
       <c r="R111" s="8">
         <v>2.8539235294117646</v>
       </c>
-      <c r="S111" s="8"/>
+      <c r="S111" s="8">
+        <v>7</v>
+      </c>
       <c r="T111" s="9">
         <v>0.70588235294117652</v>
       </c>
-      <c r="U111" s="9"/>
-      <c r="V111" s="9"/>
-      <c r="W111" s="9"/>
-      <c r="X111" s="9"/>
-      <c r="Y111" s="9"/>
-      <c r="Z111" s="9"/>
-      <c r="AA111" s="9"/>
-      <c r="AB111" s="9"/>
-      <c r="AC111" s="9"/>
-      <c r="AD111" s="6"/>
-      <c r="AE111" s="6"/>
-      <c r="AF111" s="6"/>
-      <c r="AG111" s="6"/>
-      <c r="AH111" s="6"/>
-      <c r="AI111" s="6"/>
-      <c r="AJ111" s="6"/>
-      <c r="AK111" s="6"/>
-      <c r="AL111" s="6"/>
-      <c r="AM111" s="6"/>
-      <c r="AN111" s="9"/>
-      <c r="AO111" s="6"/>
+      <c r="U111" s="9">
+        <v>0</v>
+      </c>
+      <c r="V111" s="9">
+        <v>0</v>
+      </c>
+      <c r="W111" s="9">
+        <v>0</v>
+      </c>
+      <c r="X111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y111" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM111" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN111" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO111" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP111" s="4">
         <v>58</v>
       </c>
@@ -28258,7 +28316,9 @@
       <c r="N179" s="6">
         <v>132</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>70</v>
+      </c>
       <c r="P179" s="7">
         <v>4.4082053846153846</v>
       </c>
@@ -28268,31 +28328,75 @@
       <c r="R179" s="8">
         <v>1.8164285714285715</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.7857142857142857</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>

--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-12).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-12).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>26</t>
+    <t>20</t>
   </si>
   <si>
-    <t>R$ 9.149,02</t>
+    <t>R$ 9.120,70</t>
   </si>
   <si>
-    <t>96.9</t>
+    <t>96.6</t>
   </si>
   <si>
-    <t>60.8</t>
+    <t>60.5</t>
   </si>
   <si>
-    <t>5.91</t>
+    <t>5.92</t>
   </si>
   <si>
-    <t>19.7</t>
+    <t>19.8</t>
   </si>
   <si>
-    <t>7.1</t>
+    <t>7.2</t>
   </si>
   <si>
-    <t>6.3</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>35.0%</t>
+    <t>36.2%</t>
   </si>
   <si>
-    <t>16.4%</t>
+    <t>16.3%</t>
   </si>
   <si>
     <t>1.7%</t>
@@ -980,7 +980,7 @@
     <t>0.1%</t>
   </si>
   <si>
-    <t>6.2%</t>
+    <t>6.1%</t>
   </si>
   <si>
     <t>2.3%</t>
@@ -989,10 +989,10 @@
     <t>4.4%</t>
   </si>
   <si>
-    <t>2270.0</t>
+    <t>2274.0</t>
   </si>
   <si>
-    <t>1864.0</t>
+    <t>1867.0</t>
   </si>
   <si>
     <t>192.0</t>
@@ -1004,19 +1004,19 @@
     <t>395.0</t>
   </si>
   <si>
-    <t>137.0</t>
+    <t>138.0</t>
   </si>
   <si>
     <t>15.0</t>
   </si>
   <si>
-    <t>701.0</t>
+    <t>702.0</t>
   </si>
   <si>
     <t>264.0</t>
   </si>
   <si>
-    <t>496.0</t>
+    <t>498.0</t>
   </si>
   <si>
     <t>0.6%</t>
@@ -2209,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2239,14 +2239,26 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
+      <c r="M6" s="5">
+        <v>15715.4</v>
+      </c>
+      <c r="N6" s="6">
+        <v>171</v>
+      </c>
       <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
+      <c r="P6" s="7">
+        <v>4.2420118343195261</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>14.417874637681159</v>
+      </c>
+      <c r="R6" s="8">
+        <v>3.1830920289855071</v>
+      </c>
       <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
+      <c r="T6" s="9">
+        <v>0.67391304347826086</v>
+      </c>
       <c r="U6" s="9"/>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
@@ -4961,7 +4973,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -4991,14 +5003,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>11579.02</v>
+      </c>
+      <c r="N24" s="6">
+        <v>133</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>3.9064596899224804</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>20.406632653061223</v>
+      </c>
+      <c r="R24" s="8">
+        <v>9.3943877551020414</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.27551020408163263</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6785,7 +6809,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6815,35 +6839,93 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
-      <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
-      <c r="U36" s="9"/>
-      <c r="V36" s="9"/>
-      <c r="W36" s="9"/>
-      <c r="X36" s="9"/>
-      <c r="Y36" s="9"/>
-      <c r="Z36" s="9"/>
-      <c r="AA36" s="9"/>
-      <c r="AB36" s="9"/>
-      <c r="AC36" s="9"/>
-      <c r="AD36" s="6"/>
-      <c r="AE36" s="6"/>
-      <c r="AF36" s="6"/>
-      <c r="AG36" s="6"/>
-      <c r="AH36" s="6"/>
-      <c r="AI36" s="6"/>
-      <c r="AJ36" s="6"/>
-      <c r="AK36" s="6"/>
-      <c r="AL36" s="6"/>
-      <c r="AM36" s="6"/>
-      <c r="AN36" s="9"/>
-      <c r="AO36" s="6"/>
+      <c r="M36" s="5">
+        <v>6226.3299999999999</v>
+      </c>
+      <c r="N36" s="6">
+        <v>66</v>
+      </c>
+      <c r="O36" s="6">
+        <v>45</v>
+      </c>
+      <c r="P36" s="7">
+        <v>6.8199459016393442</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>17.934073333333334</v>
+      </c>
+      <c r="R36" s="8">
+        <v>4.0488636363636363</v>
+      </c>
+      <c r="S36" s="8">
+        <v>7</v>
+      </c>
+      <c r="T36" s="9">
+        <v>0.37777777777777777</v>
+      </c>
+      <c r="U36" s="9">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="V36" s="9">
+        <v>0</v>
+      </c>
+      <c r="W36" s="9">
+        <v>0</v>
+      </c>
+      <c r="X36" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="9">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="Z36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="9">
+        <v>0.022222222222222223</v>
+      </c>
+      <c r="AB36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK36" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM36" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP36" s="4">
         <v>58</v>
       </c>
@@ -9074,7 +9156,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9104,35 +9186,93 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
-      <c r="U51" s="9"/>
-      <c r="V51" s="9"/>
-      <c r="W51" s="9"/>
-      <c r="X51" s="9"/>
-      <c r="Y51" s="9"/>
-      <c r="Z51" s="9"/>
-      <c r="AA51" s="9"/>
-      <c r="AB51" s="9"/>
-      <c r="AC51" s="9"/>
-      <c r="AD51" s="6"/>
-      <c r="AE51" s="6"/>
-      <c r="AF51" s="6"/>
-      <c r="AG51" s="6"/>
-      <c r="AH51" s="6"/>
-      <c r="AI51" s="6"/>
-      <c r="AJ51" s="6"/>
-      <c r="AK51" s="6"/>
-      <c r="AL51" s="6"/>
-      <c r="AM51" s="6"/>
-      <c r="AN51" s="9"/>
-      <c r="AO51" s="6"/>
+      <c r="M51" s="5">
+        <v>1237.9000000000001</v>
+      </c>
+      <c r="N51" s="6">
+        <v>12</v>
+      </c>
+      <c r="O51" s="6">
+        <v>9</v>
+      </c>
+      <c r="P51" s="7">
+        <v>8.7987153846153845</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>46.496299999999998</v>
+      </c>
+      <c r="R51" s="8">
+        <v>31.411111111111111</v>
+      </c>
+      <c r="S51" s="8">
+        <v>7</v>
+      </c>
+      <c r="T51" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="U51" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="V51" s="9">
+        <v>0</v>
+      </c>
+      <c r="W51" s="9">
+        <v>0</v>
+      </c>
+      <c r="X51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="AD51" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN51" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP51" s="4">
         <v>58</v>
       </c>
@@ -14776,7 +14916,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14804,14 +14944,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>7832.1000000000004</v>
+      </c>
+      <c r="N89" s="6">
+        <v>75</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>5.0921175675675681</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>17.505714285714287</v>
+      </c>
+      <c r="R89" s="8">
+        <v>3.8583323529411766</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.31428571428571428</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -25105,7 +25257,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -25135,14 +25287,26 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
+      <c r="M158" s="5">
+        <v>6836.3599999999997</v>
+      </c>
+      <c r="N158" s="6">
+        <v>71</v>
+      </c>
       <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
+      <c r="P158" s="7">
+        <v>8.8992957746478876</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>20.543677586206897</v>
+      </c>
+      <c r="R158" s="8">
+        <v>4.5672413793103441</v>
+      </c>
       <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
+      <c r="T158" s="9">
+        <v>0.13793103448275862</v>
+      </c>
       <c r="U158" s="9"/>
       <c r="V158" s="9"/>
       <c r="W158" s="9"/>
